--- a/trade_journal.xlsx
+++ b/trade_journal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,21 @@
           <t>why_lose</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>risk_dollar</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>risk_percent</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>real_risk_pct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -579,6 +594,9 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -635,6 +653,74 @@
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADAUSDT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.2174</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ntcn</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>open: 2026-04-07T15:49:36.934579, close: None</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
